--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/33.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/33.xlsx
@@ -426,13 +426,13 @@
         <v>-11.74085510321187</v>
       </c>
       <c r="E2">
-        <v>-16.37161754615195</v>
+        <v>-15.37307544203861</v>
       </c>
       <c r="F2">
-        <v>-1.738181692624572</v>
+        <v>-0.7661207099310473</v>
       </c>
       <c r="G2">
-        <v>-10.51172811060069</v>
+        <v>-9.858719692433908</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.48197363344884</v>
       </c>
       <c r="E3">
-        <v>-17.13524506111738</v>
+        <v>-16.67721708608557</v>
       </c>
       <c r="F3">
-        <v>-1.959634948986783</v>
+        <v>-1.011288468300603</v>
       </c>
       <c r="G3">
-        <v>-10.25866338848772</v>
+        <v>-9.9060869780098</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.23856533855472</v>
       </c>
       <c r="E4">
-        <v>-17.30864485934509</v>
+        <v>-16.98700093600229</v>
       </c>
       <c r="F4">
-        <v>-1.886220059546274</v>
+        <v>-0.5943587289605698</v>
       </c>
       <c r="G4">
-        <v>-10.63827702438487</v>
+        <v>-10.46962790297778</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.03196273673486</v>
       </c>
       <c r="E5">
-        <v>-19.10426178744451</v>
+        <v>-18.24597105182274</v>
       </c>
       <c r="F5">
-        <v>-2.131645440178101</v>
+        <v>-0.7954995882387346</v>
       </c>
       <c r="G5">
-        <v>-10.12356995666668</v>
+        <v>-9.866522648269971</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.82726084268853</v>
       </c>
       <c r="E6">
-        <v>-19.52765146479166</v>
+        <v>-18.51357669483201</v>
       </c>
       <c r="F6">
-        <v>-2.145702835003608</v>
+        <v>-1.046315155560577</v>
       </c>
       <c r="G6">
-        <v>-9.770007003618058</v>
+        <v>-10.28337992148392</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.61024737649738</v>
       </c>
       <c r="E7">
-        <v>-18.956361826354</v>
+        <v>-19.24520601245925</v>
       </c>
       <c r="F7">
-        <v>-1.929115408765441</v>
+        <v>-0.6701410924382798</v>
       </c>
       <c r="G7">
-        <v>-9.81251771888784</v>
+        <v>-9.604284404467682</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.35305208575618</v>
       </c>
       <c r="E8">
-        <v>-20.35577350657433</v>
+        <v>-20.42036313134574</v>
       </c>
       <c r="F8">
-        <v>-1.958597832998478</v>
+        <v>-0.8545414748732694</v>
       </c>
       <c r="G8">
-        <v>-9.127334108624881</v>
+        <v>-9.758698180055907</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.03663682466116</v>
       </c>
       <c r="E9">
-        <v>-20.7312972136604</v>
+        <v>-19.85124263195776</v>
       </c>
       <c r="F9">
-        <v>-2.213706828569031</v>
+        <v>-0.3487486223979192</v>
       </c>
       <c r="G9">
-        <v>-9.604747880843179</v>
+        <v>-9.636999215486759</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.648224667475327</v>
       </c>
       <c r="E10">
-        <v>-21.77827134728577</v>
+        <v>-20.58531732554914</v>
       </c>
       <c r="F10">
-        <v>-1.870751955033799</v>
+        <v>-1.000811277389995</v>
       </c>
       <c r="G10">
-        <v>-9.056594371541735</v>
+        <v>-9.702346073886433</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.182488176320286</v>
       </c>
       <c r="E11">
-        <v>-21.84644299499724</v>
+        <v>-22.04320519063052</v>
       </c>
       <c r="F11">
-        <v>-1.896816535362886</v>
+        <v>-0.2652748675852158</v>
       </c>
       <c r="G11">
-        <v>-8.49291109311557</v>
+        <v>-8.826832579479698</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.655939302317734</v>
       </c>
       <c r="E12">
-        <v>-24.06146454331706</v>
+        <v>-22.97713502760241</v>
       </c>
       <c r="F12">
-        <v>-1.441314696278896</v>
+        <v>-0.4894667065810824</v>
       </c>
       <c r="G12">
-        <v>-8.576131586881768</v>
+        <v>-8.240283363013784</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.088919076139337</v>
       </c>
       <c r="E13">
-        <v>-23.80851757067061</v>
+        <v>-23.16121296754021</v>
       </c>
       <c r="F13">
-        <v>-1.039066112418679</v>
+        <v>-0.4138665839319883</v>
       </c>
       <c r="G13">
-        <v>-8.030126621635311</v>
+        <v>-7.568398214182079</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.527635988980458</v>
       </c>
       <c r="E14">
-        <v>-23.84175204141291</v>
+        <v>-24.07162191051626</v>
       </c>
       <c r="F14">
-        <v>-1.597188590463679</v>
+        <v>0.1392069947929492</v>
       </c>
       <c r="G14">
-        <v>-8.262583197766316</v>
+        <v>-7.593915899198782</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.016254639304698</v>
       </c>
       <c r="E15">
-        <v>-26.92754027124563</v>
+        <v>-24.58967028004573</v>
       </c>
       <c r="F15">
-        <v>-0.6328140289007312</v>
+        <v>0.5273261158636156</v>
       </c>
       <c r="G15">
-        <v>-7.622823582847698</v>
+        <v>-7.639018771625812</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.599648420303089</v>
       </c>
       <c r="E16">
-        <v>-27.26667768968007</v>
+        <v>-25.61324578847347</v>
       </c>
       <c r="F16">
-        <v>-0.6914433885686719</v>
+        <v>0.4526728171559213</v>
       </c>
       <c r="G16">
-        <v>-6.450099241561812</v>
+        <v>-7.134852480904664</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.32128969600829</v>
       </c>
       <c r="E17">
-        <v>-27.09086874328028</v>
+        <v>-26.83636850404921</v>
       </c>
       <c r="F17">
-        <v>-0.3305030019838573</v>
+        <v>1.071162569679936</v>
       </c>
       <c r="G17">
-        <v>-6.807767271079132</v>
+        <v>-6.776118455723699</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.205587419204026</v>
       </c>
       <c r="E18">
-        <v>-27.16620896534589</v>
+        <v>-27.41678754608632</v>
       </c>
       <c r="F18">
-        <v>0.2519105217808359</v>
+        <v>1.191496188815009</v>
       </c>
       <c r="G18">
-        <v>-6.403046457812151</v>
+        <v>-6.773579267295078</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.271251326106835</v>
       </c>
       <c r="E19">
-        <v>-28.72946083516374</v>
+        <v>-28.06113052721572</v>
       </c>
       <c r="F19">
-        <v>0.5405294638968369</v>
+        <v>1.509763228644607</v>
       </c>
       <c r="G19">
-        <v>-6.237721124126486</v>
+        <v>-5.5844677255898</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.51264206599185</v>
       </c>
       <c r="E20">
-        <v>-30.18802344287226</v>
+        <v>-28.43120648007055</v>
       </c>
       <c r="F20">
-        <v>0.4774410024996265</v>
+        <v>1.710473336873316</v>
       </c>
       <c r="G20">
-        <v>-5.989771194871692</v>
+        <v>-6.014342063864164</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.917161608168321</v>
       </c>
       <c r="E21">
-        <v>-30.22244437380456</v>
+        <v>-29.04964206140206</v>
       </c>
       <c r="F21">
-        <v>0.7337337350887796</v>
+        <v>1.991781936659611</v>
       </c>
       <c r="G21">
-        <v>-6.08099327720631</v>
+        <v>-5.255253834982516</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.455935776269522</v>
       </c>
       <c r="E22">
-        <v>-30.46261199280136</v>
+        <v>-29.16991833104579</v>
       </c>
       <c r="F22">
-        <v>1.126303674214688</v>
+        <v>2.170802072813418</v>
       </c>
       <c r="G22">
-        <v>-6.169312011102987</v>
+        <v>-5.270131426636</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.090196565206861</v>
       </c>
       <c r="E23">
-        <v>-31.85510416473797</v>
+        <v>-30.31741553069342</v>
       </c>
       <c r="F23">
-        <v>1.13668146103696</v>
+        <v>2.1974572791007</v>
       </c>
       <c r="G23">
-        <v>-6.053581960141145</v>
+        <v>-5.59259511488871</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.779865030529193</v>
       </c>
       <c r="E24">
-        <v>-31.42658599057714</v>
+        <v>-31.01638096530334</v>
       </c>
       <c r="F24">
-        <v>1.604589758712677</v>
+        <v>2.333352608264765</v>
       </c>
       <c r="G24">
-        <v>-6.415212712668972</v>
+        <v>-5.709139560053213</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.471819393440935</v>
       </c>
       <c r="E25">
-        <v>-31.80384636744515</v>
+        <v>-30.50533814506373</v>
       </c>
       <c r="F25">
-        <v>1.352704769073821</v>
+        <v>1.878380095951164</v>
       </c>
       <c r="G25">
-        <v>-6.022879960809944</v>
+        <v>-5.117257054723535</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.11931678600264</v>
       </c>
       <c r="E26">
-        <v>-31.23880149466407</v>
+        <v>-30.6777145081657</v>
       </c>
       <c r="F26">
-        <v>0.7470671368042404</v>
+        <v>2.02973938779069</v>
       </c>
       <c r="G26">
-        <v>-5.890041010501148</v>
+        <v>-4.633619456891408</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.66918548820348</v>
       </c>
       <c r="E27">
-        <v>-31.88250143248438</v>
+        <v>-31.3966256065424</v>
       </c>
       <c r="F27">
-        <v>1.220669632006802</v>
+        <v>1.903569091935492</v>
       </c>
       <c r="G27">
-        <v>-6.0824929543356</v>
+        <v>-5.371096444492693</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.08002707145132</v>
       </c>
       <c r="E28">
-        <v>-32.16889118567747</v>
+        <v>-30.78504160638449</v>
       </c>
       <c r="F28">
-        <v>1.455516760904878</v>
+        <v>2.31003737934557</v>
       </c>
       <c r="G28">
-        <v>-6.374982963275749</v>
+        <v>-5.385868098688921</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.31704063294605</v>
       </c>
       <c r="E29">
-        <v>-31.07473940984018</v>
+        <v>-31.47277868969239</v>
       </c>
       <c r="F29">
-        <v>1.198235786004185</v>
+        <v>2.18170338783426</v>
       </c>
       <c r="G29">
-        <v>-5.978581550948956</v>
+        <v>-5.734339432698146</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.36339703050652</v>
       </c>
       <c r="E30">
-        <v>-31.20139856359772</v>
+        <v>-30.7734147493698</v>
       </c>
       <c r="F30">
-        <v>1.463931316982516</v>
+        <v>1.825820184243536</v>
       </c>
       <c r="G30">
-        <v>-6.810286596234517</v>
+        <v>-5.599431391427306</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.21590173193167</v>
       </c>
       <c r="E31">
-        <v>-30.90895197641937</v>
+        <v>-29.90811846445816</v>
       </c>
       <c r="F31">
-        <v>0.8694087185236994</v>
+        <v>1.715682111102119</v>
       </c>
       <c r="G31">
-        <v>-6.098880154754992</v>
+        <v>-5.324709080396425</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.88331357387833</v>
       </c>
       <c r="E32">
-        <v>-30.69356869566656</v>
+        <v>-30.59190445419436</v>
       </c>
       <c r="F32">
-        <v>0.9041123424965819</v>
+        <v>1.864659018291193</v>
       </c>
       <c r="G32">
-        <v>-5.905676717083126</v>
+        <v>-5.765471802949452</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.39010448315947</v>
       </c>
       <c r="E33">
-        <v>-31.35601651587861</v>
+        <v>-30.04839473955676</v>
       </c>
       <c r="F33">
-        <v>0.934954117637613</v>
+        <v>1.918073805158511</v>
       </c>
       <c r="G33">
-        <v>-6.202576372681584</v>
+        <v>-5.42788885321889</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.767086539846638</v>
       </c>
       <c r="E34">
-        <v>-30.82298116162076</v>
+        <v>-30.06260056251882</v>
       </c>
       <c r="F34">
-        <v>0.9076395308977021</v>
+        <v>1.639576684337317</v>
       </c>
       <c r="G34">
-        <v>-6.516465747987581</v>
+        <v>-5.74948848908585</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.057594647429259</v>
       </c>
       <c r="E35">
-        <v>-29.57637604407825</v>
+        <v>-29.56438011643193</v>
       </c>
       <c r="F35">
-        <v>1.357885378810929</v>
+        <v>1.541449938536493</v>
       </c>
       <c r="G35">
-        <v>-6.264751728454636</v>
+        <v>-5.37361245910254</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.299245844040023</v>
       </c>
       <c r="E36">
-        <v>-28.82425085309229</v>
+        <v>-29.80162686969378</v>
       </c>
       <c r="F36">
-        <v>0.8987362380524131</v>
+        <v>1.781436258801538</v>
       </c>
       <c r="G36">
-        <v>-6.771569766152741</v>
+        <v>-5.225962128051044</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.540590943923758</v>
       </c>
       <c r="E37">
-        <v>-29.66639757887673</v>
+        <v>-28.69095974915053</v>
       </c>
       <c r="F37">
-        <v>0.7270521236177987</v>
+        <v>1.665289208520214</v>
       </c>
       <c r="G37">
-        <v>-6.165796211740281</v>
+        <v>-5.272822900159428</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.815663679519275</v>
       </c>
       <c r="E38">
-        <v>-29.86474700464969</v>
+        <v>-28.35667232637831</v>
       </c>
       <c r="F38">
-        <v>1.10935527715341</v>
+        <v>1.923857466364857</v>
       </c>
       <c r="G38">
-        <v>-6.449453685181654</v>
+        <v>-5.154954236779217</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.159918577865414</v>
       </c>
       <c r="E39">
-        <v>-28.21839537255409</v>
+        <v>-27.70991566860283</v>
       </c>
       <c r="F39">
-        <v>0.9997937477243416</v>
+        <v>1.644679427538562</v>
       </c>
       <c r="G39">
-        <v>-5.350624030877841</v>
+        <v>-4.851208373005546</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.596611044463923</v>
       </c>
       <c r="E40">
-        <v>-27.71225236119079</v>
+        <v>-26.58047802329778</v>
       </c>
       <c r="F40">
-        <v>0.6258471645481719</v>
+        <v>2.072506340062423</v>
       </c>
       <c r="G40">
-        <v>-5.351031227979171</v>
+        <v>-4.577542126001694</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.140051383752652</v>
       </c>
       <c r="E41">
-        <v>-27.93502158305011</v>
+        <v>-27.18930871125902</v>
       </c>
       <c r="F41">
-        <v>1.110427184572632</v>
+        <v>1.580457759534322</v>
       </c>
       <c r="G41">
-        <v>-6.072951962091421</v>
+        <v>-4.785358311683903</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.800454948190077</v>
       </c>
       <c r="E42">
-        <v>-27.41189679415804</v>
+        <v>-26.05767022758624</v>
       </c>
       <c r="F42">
-        <v>0.9063837259150581</v>
+        <v>2.022734713032618</v>
       </c>
       <c r="G42">
-        <v>-6.135779495335709</v>
+        <v>-5.29970452993831</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.573538473209993</v>
       </c>
       <c r="E43">
-        <v>-26.43942058643285</v>
+        <v>-25.98883742266965</v>
       </c>
       <c r="F43">
-        <v>0.7441297459939133</v>
+        <v>1.810616328932554</v>
       </c>
       <c r="G43">
-        <v>-5.99178400655957</v>
+        <v>-5.013729674619447</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.459085743481179</v>
       </c>
       <c r="E44">
-        <v>-26.15115604500059</v>
+        <v>-26.1570068334185</v>
       </c>
       <c r="F44">
-        <v>1.003518087567328</v>
+        <v>1.793257061639487</v>
       </c>
       <c r="G44">
-        <v>-6.963650928886794</v>
+        <v>-4.571540106938994</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.442334468603226</v>
       </c>
       <c r="E45">
-        <v>-24.96327391415255</v>
+        <v>-25.26556766806057</v>
       </c>
       <c r="F45">
-        <v>1.053819869734925</v>
+        <v>1.702042213447623</v>
       </c>
       <c r="G45">
-        <v>-6.806856871055832</v>
+        <v>-4.581547886104212</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.512788550829391</v>
       </c>
       <c r="E46">
-        <v>-25.27816588274991</v>
+        <v>-24.85549623276999</v>
       </c>
       <c r="F46">
-        <v>1.451648285133805</v>
+        <v>1.943700179131517</v>
       </c>
       <c r="G46">
-        <v>-6.690236283343926</v>
+        <v>-5.276782312624396</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.653676184986205</v>
       </c>
       <c r="E47">
-        <v>-24.5947874556744</v>
+        <v>-24.24730858811784</v>
       </c>
       <c r="F47">
-        <v>1.195594950724061</v>
+        <v>1.770163835184243</v>
       </c>
       <c r="G47">
-        <v>-6.676034042980453</v>
+        <v>-5.8017752453331</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.845106111763484</v>
       </c>
       <c r="E48">
-        <v>-24.46232506247604</v>
+        <v>-23.86865117701847</v>
       </c>
       <c r="F48">
-        <v>1.233976525965373</v>
+        <v>2.304578438161121</v>
       </c>
       <c r="G48">
-        <v>-6.369149782035553</v>
+        <v>-5.539033798608842</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.071371836535163</v>
       </c>
       <c r="E49">
-        <v>-24.71071639027076</v>
+        <v>-23.17276963320778</v>
       </c>
       <c r="F49">
-        <v>1.036785322463756</v>
+        <v>1.946394029925421</v>
       </c>
       <c r="G49">
-        <v>-6.834341020122862</v>
+        <v>-5.549587817788039</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.311856787029027</v>
       </c>
       <c r="E50">
-        <v>-23.75870435658624</v>
+        <v>-22.8442922425874</v>
       </c>
       <c r="F50">
-        <v>1.416613314199802</v>
+        <v>1.757882460070337</v>
       </c>
       <c r="G50">
-        <v>-6.638465972200803</v>
+        <v>-5.973264814812887</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.552351401215067</v>
       </c>
       <c r="E51">
-        <v>-22.94314883017485</v>
+        <v>-23.58706160627351</v>
       </c>
       <c r="F51">
-        <v>1.466688123699033</v>
+        <v>2.319111315875836</v>
       </c>
       <c r="G51">
-        <v>-6.61872187860459</v>
+        <v>-5.653303898987866</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.776668824990572</v>
       </c>
       <c r="E52">
-        <v>-23.06295413852177</v>
+        <v>-22.20839486548232</v>
       </c>
       <c r="F52">
-        <v>1.225457595594983</v>
+        <v>2.352098562590118</v>
       </c>
       <c r="G52">
-        <v>-6.635807604132768</v>
+        <v>-6.11824022506865</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.975090678720741</v>
       </c>
       <c r="E53">
-        <v>-22.05566302262562</v>
+        <v>-21.97411426269549</v>
       </c>
       <c r="F53">
-        <v>1.492548097279627</v>
+        <v>2.208809225988665</v>
       </c>
       <c r="G53">
-        <v>-6.625945488971279</v>
+        <v>-5.73331978467205</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.142337606676549</v>
       </c>
       <c r="E54">
-        <v>-22.12348144936449</v>
+        <v>-20.76974848645953</v>
       </c>
       <c r="F54">
-        <v>0.9752276840269194</v>
+        <v>2.304999248801743</v>
       </c>
       <c r="G54">
-        <v>-7.351504512631188</v>
+        <v>-6.117568184324178</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.272637601468441</v>
       </c>
       <c r="E55">
-        <v>-21.23294345033409</v>
+        <v>-20.82686612911827</v>
       </c>
       <c r="F55">
-        <v>1.417640489779274</v>
+        <v>2.233574097862759</v>
       </c>
       <c r="G55">
-        <v>-6.986828058207232</v>
+        <v>-6.008558540807057</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.370818638019149</v>
       </c>
       <c r="E56">
-        <v>-21.57824412189296</v>
+        <v>-20.21229786458931</v>
       </c>
       <c r="F56">
-        <v>1.473971129904446</v>
+        <v>2.256080840196821</v>
       </c>
       <c r="G56">
-        <v>-7.555003746930188</v>
+        <v>-6.541854321728252</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.437974070970811</v>
       </c>
       <c r="E57">
-        <v>-21.14866402057734</v>
+        <v>-19.32604833044418</v>
       </c>
       <c r="F57">
-        <v>1.653978680002389</v>
+        <v>2.652532508972248</v>
       </c>
       <c r="G57">
-        <v>-7.27441514920372</v>
+        <v>-6.375366986558304</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.482502015671384</v>
       </c>
       <c r="E58">
-        <v>-20.57799478307873</v>
+        <v>-20.40809549525896</v>
       </c>
       <c r="F58">
-        <v>1.750003029334908</v>
+        <v>2.550898455587971</v>
       </c>
       <c r="G58">
-        <v>-6.991320468504023</v>
+        <v>-6.286833067201575</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.509792087119075</v>
       </c>
       <c r="E59">
-        <v>-20.20147934018499</v>
+        <v>-19.47301542588911</v>
       </c>
       <c r="F59">
-        <v>1.659735833451846</v>
+        <v>2.530964622407004</v>
       </c>
       <c r="G59">
-        <v>-7.77725391116362</v>
+        <v>-7.050119067827018</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.528724303672639</v>
       </c>
       <c r="E60">
-        <v>-20.21745126801004</v>
+        <v>-19.11673320486164</v>
       </c>
       <c r="F60">
-        <v>1.968158555066575</v>
+        <v>2.369810714396777</v>
       </c>
       <c r="G60">
-        <v>-7.604022994730177</v>
+        <v>-7.146839966302365</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.54687985206404</v>
       </c>
       <c r="E61">
-        <v>-20.8028561599296</v>
+        <v>-18.92545046277764</v>
       </c>
       <c r="F61">
-        <v>1.996990710888414</v>
+        <v>2.37391278977544</v>
       </c>
       <c r="G61">
-        <v>-7.861477500228219</v>
+        <v>-7.799871558287921</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.568829572220602</v>
       </c>
       <c r="E62">
-        <v>-18.81993248992492</v>
+        <v>-18.1354898714576</v>
       </c>
       <c r="F62">
-        <v>1.556617345681752</v>
+        <v>2.564841535711892</v>
       </c>
       <c r="G62">
-        <v>-8.796322591789773</v>
+        <v>-7.406568816585886</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.601773160298361</v>
       </c>
       <c r="E63">
-        <v>-18.8150824942627</v>
+        <v>-18.42659829456668</v>
       </c>
       <c r="F63">
-        <v>1.650242743015764</v>
+        <v>2.03312741046814</v>
       </c>
       <c r="G63">
-        <v>-8.743903413720954</v>
+        <v>-8.18724842347466</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.644893327888093</v>
       </c>
       <c r="E64">
-        <v>-18.22197013958208</v>
+        <v>-18.08592572344365</v>
       </c>
       <c r="F64">
-        <v>1.54496718652878</v>
+        <v>2.094186371728492</v>
       </c>
       <c r="G64">
-        <v>-8.962790063686485</v>
+        <v>-8.39302531310468</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.701581164650444</v>
       </c>
       <c r="E65">
-        <v>-18.46181170845033</v>
+        <v>-17.36037814640871</v>
       </c>
       <c r="F65">
-        <v>1.529645703046601</v>
+        <v>2.445492017051345</v>
       </c>
       <c r="G65">
-        <v>-8.558870402440009</v>
+        <v>-8.182560690991053</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.767824434596495</v>
       </c>
       <c r="E66">
-        <v>-18.4833446023568</v>
+        <v>-18.23298338836874</v>
       </c>
       <c r="F66">
-        <v>1.698228409925133</v>
+        <v>2.22126787172677</v>
       </c>
       <c r="G66">
-        <v>-9.018466818565949</v>
+        <v>-8.366021193140844</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.843578951093045</v>
       </c>
       <c r="E67">
-        <v>-18.92454476797611</v>
+        <v>-17.62403043160929</v>
       </c>
       <c r="F67">
-        <v>1.305204525462491</v>
+        <v>1.942996066839137</v>
       </c>
       <c r="G67">
-        <v>-8.863000289496235</v>
+        <v>-8.375757507571841</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.923651270645164</v>
       </c>
       <c r="E68">
-        <v>-18.19733524098036</v>
+        <v>-18.07012587763089</v>
       </c>
       <c r="F68">
-        <v>1.195411053160639</v>
+        <v>2.163181092707662</v>
       </c>
       <c r="G68">
-        <v>-8.904680057835659</v>
+        <v>-8.867671469252146</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.004818513401837</v>
       </c>
       <c r="E69">
-        <v>-18.11578648105023</v>
+        <v>-16.28956159713296</v>
       </c>
       <c r="F69">
-        <v>1.564843033991552</v>
+        <v>2.516241220189645</v>
       </c>
       <c r="G69">
-        <v>-9.305567259368164</v>
+        <v>-8.95559624822965</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.08422782432432</v>
       </c>
       <c r="E70">
-        <v>-18.73092080483015</v>
+        <v>-17.39168348722374</v>
       </c>
       <c r="F70">
-        <v>1.676077865574275</v>
+        <v>1.99099167415734</v>
       </c>
       <c r="G70">
-        <v>-9.122891356511179</v>
+        <v>-9.110394047100431</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.154803313428344</v>
       </c>
       <c r="E71">
-        <v>-17.81085715526974</v>
+        <v>-16.87661938206532</v>
       </c>
       <c r="F71">
-        <v>1.52189881109562</v>
+        <v>1.905741071265632</v>
       </c>
       <c r="G71">
-        <v>-9.529396553823828</v>
+        <v>-8.527400356543696</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.216883306591494</v>
       </c>
       <c r="E72">
-        <v>-18.04239350280792</v>
+        <v>-16.17760413424132</v>
       </c>
       <c r="F72">
-        <v>1.355425127624614</v>
+        <v>1.644591620593866</v>
       </c>
       <c r="G72">
-        <v>-9.232506829861988</v>
+        <v>-8.731548457768394</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.265115183902042</v>
       </c>
       <c r="E73">
-        <v>-17.6911061886109</v>
+        <v>-17.47900152303964</v>
       </c>
       <c r="F73">
-        <v>1.430813188218591</v>
+        <v>2.230033655583194</v>
       </c>
       <c r="G73">
-        <v>-9.854323287957756</v>
+        <v>-8.991350140053779</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.3016300568029</v>
       </c>
       <c r="E74">
-        <v>-18.07320976843011</v>
+        <v>-17.31190988910462</v>
       </c>
       <c r="F74">
-        <v>1.321258285728746</v>
+        <v>1.934884693230924</v>
       </c>
       <c r="G74">
-        <v>-9.029411482118778</v>
+        <v>-8.822403069548152</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.323740321436113</v>
       </c>
       <c r="E75">
-        <v>-18.19489892196423</v>
+        <v>-16.70755333346296</v>
       </c>
       <c r="F75">
-        <v>1.671009913803947</v>
+        <v>1.777617485074632</v>
       </c>
       <c r="G75">
-        <v>-8.472922019149451</v>
+        <v>-8.898529064223693</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.334663314588947</v>
       </c>
       <c r="E76">
-        <v>-17.85406785425093</v>
+        <v>-16.40578941101383</v>
       </c>
       <c r="F76">
-        <v>1.142067505889962</v>
+        <v>1.413588116444779</v>
       </c>
       <c r="G76">
-        <v>-8.900051915171758</v>
+        <v>-8.418109316655737</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.336449246148295</v>
       </c>
       <c r="E77">
-        <v>-18.65475640049514</v>
+        <v>-17.13060790373353</v>
       </c>
       <c r="F77">
-        <v>1.16493375967684</v>
+        <v>1.160419157331583</v>
       </c>
       <c r="G77">
-        <v>-7.897747837156474</v>
+        <v>-7.969636333541747</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.329804332557584</v>
       </c>
       <c r="E78">
-        <v>-18.67797841520647</v>
+        <v>-17.80446747844492</v>
       </c>
       <c r="F78">
-        <v>1.080465135613374</v>
+        <v>1.440629341941766</v>
       </c>
       <c r="G78">
-        <v>-8.42022806580087</v>
+        <v>-7.918150729315002</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.321521544123065</v>
       </c>
       <c r="E79">
-        <v>-18.67114947640291</v>
+        <v>-17.63435535234678</v>
       </c>
       <c r="F79">
-        <v>1.044626648298656</v>
+        <v>1.138727528521875</v>
       </c>
       <c r="G79">
-        <v>-8.345181308971132</v>
+        <v>-8.145850051506073</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.311907372541639</v>
       </c>
       <c r="E80">
-        <v>-18.38359137691584</v>
+        <v>-18.11283844447124</v>
       </c>
       <c r="F80">
-        <v>0.4684581863836687</v>
+        <v>1.469771307172252</v>
       </c>
       <c r="G80">
-        <v>-8.573138853714267</v>
+        <v>-7.403715126331035</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.307678315698675</v>
       </c>
       <c r="E81">
-        <v>-18.84668218588823</v>
+        <v>-18.07033418743524</v>
       </c>
       <c r="F81">
-        <v>0.3765499946756607</v>
+        <v>1.562389409744459</v>
       </c>
       <c r="G81">
-        <v>-8.609803145561695</v>
+        <v>-7.513631859325916</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.309147404076674</v>
       </c>
       <c r="E82">
-        <v>-20.98976439612219</v>
+        <v>-20.17624668301425</v>
       </c>
       <c r="F82">
-        <v>0.8321321853977216</v>
+        <v>0.8638122683503859</v>
       </c>
       <c r="G82">
-        <v>-8.136583834541653</v>
+        <v>-7.503650564525014</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.322380194172371</v>
       </c>
       <c r="E83">
-        <v>-19.70493669371794</v>
+        <v>-20.51304740886073</v>
       </c>
       <c r="F83">
-        <v>0.1274466627754046</v>
+        <v>0.9045613176288992</v>
       </c>
       <c r="G83">
-        <v>-8.28622711400779</v>
+        <v>-7.504306052541789</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.350766819660229</v>
       </c>
       <c r="E84">
-        <v>-20.98678013175114</v>
+        <v>-20.89572610487891</v>
       </c>
       <c r="F84">
-        <v>0.619942561701017</v>
+        <v>0.8189777110412655</v>
       </c>
       <c r="G84">
-        <v>-7.279867617706899</v>
+        <v>-7.094503551872027</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.39816982861401</v>
       </c>
       <c r="E85">
-        <v>-22.56059240295487</v>
+        <v>-22.86312163751129</v>
       </c>
       <c r="F85">
-        <v>0.08421002618628438</v>
+        <v>0.898158037605259</v>
       </c>
       <c r="G85">
-        <v>-7.920223130822586</v>
+        <v>-7.494635949021578</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.474484629812435</v>
       </c>
       <c r="E86">
-        <v>-23.86769114052884</v>
+        <v>-23.09173259084052</v>
       </c>
       <c r="F86">
-        <v>0.3302724213508635</v>
+        <v>0.4492657420282069</v>
       </c>
       <c r="G86">
-        <v>-7.205883545995267</v>
+        <v>-6.339129755085442</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.581648507343255</v>
       </c>
       <c r="E87">
-        <v>-24.40650256338348</v>
+        <v>-24.86160967268035</v>
       </c>
       <c r="F87">
-        <v>-0.1512310421395995</v>
+        <v>0.6688369476512579</v>
       </c>
       <c r="G87">
-        <v>-7.569215918930279</v>
+        <v>-7.007287229639927</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.732316840065482</v>
       </c>
       <c r="E88">
-        <v>-26.15194399947793</v>
+        <v>-25.1003327084687</v>
       </c>
       <c r="F88">
-        <v>-0.05774315379445289</v>
+        <v>0.4032706419877644</v>
       </c>
       <c r="G88">
-        <v>-6.254498968919513</v>
+        <v>-6.252459672867322</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.92978669104645</v>
       </c>
       <c r="E89">
-        <v>-27.9957076632269</v>
+        <v>-27.1354560983598</v>
       </c>
       <c r="F89">
-        <v>-0.3404525228588822</v>
+        <v>0.06712080666653059</v>
       </c>
       <c r="G89">
-        <v>-6.222787253198835</v>
+        <v>-5.991390051640396</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.183066272133861</v>
       </c>
       <c r="E90">
-        <v>-29.57464163853331</v>
+        <v>-28.68690676491366</v>
       </c>
       <c r="F90">
-        <v>-0.6128122695927344</v>
+        <v>0.02870195489209232</v>
       </c>
       <c r="G90">
-        <v>-6.001265408984042</v>
+        <v>-5.428047759404776</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.495952675057797</v>
       </c>
       <c r="E91">
-        <v>-30.95610244778724</v>
+        <v>-29.76402695000809</v>
       </c>
       <c r="F91">
-        <v>-0.9926684258204758</v>
+        <v>-0.668818189696009</v>
       </c>
       <c r="G91">
-        <v>-6.66632752345931</v>
+        <v>-6.030007565355994</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.869707800583944</v>
       </c>
       <c r="E92">
-        <v>-32.08402305429971</v>
+        <v>-31.78167948717761</v>
       </c>
       <c r="F92">
-        <v>-1.223387799950402</v>
+        <v>-0.4823543440606459</v>
       </c>
       <c r="G92">
-        <v>-6.269472566393636</v>
+        <v>-6.228746235169522</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.309800049257129</v>
       </c>
       <c r="E93">
-        <v>-33.68270344051657</v>
+        <v>-33.42128822147578</v>
       </c>
       <c r="F93">
-        <v>-1.026394576258055</v>
+        <v>-0.6358649060452418</v>
       </c>
       <c r="G93">
-        <v>-6.016311838460029</v>
+        <v>-5.548733697038907</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.80406344353336</v>
       </c>
       <c r="E94">
-        <v>-35.90106926689105</v>
+        <v>-34.6818319820139</v>
       </c>
       <c r="F94">
-        <v>-1.505792329810602</v>
+        <v>-1.076517431066647</v>
       </c>
       <c r="G94">
-        <v>-6.300654594828032</v>
+        <v>-5.767997749195916</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.35345587227848</v>
       </c>
       <c r="E95">
-        <v>-38.08118986603375</v>
+        <v>-37.32377994588085</v>
       </c>
       <c r="F95">
-        <v>-1.989240799962838</v>
+        <v>-1.516585957069079</v>
       </c>
       <c r="G95">
-        <v>-6.370017144966842</v>
+        <v>-6.663156020832687</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.94337572788316</v>
       </c>
       <c r="E96">
-        <v>-39.79442479498564</v>
+        <v>-40.02152550223331</v>
       </c>
       <c r="F96">
-        <v>-2.316035882204257</v>
+        <v>-1.374573963002743</v>
       </c>
       <c r="G96">
-        <v>-5.915154808962059</v>
+        <v>-5.920471545098128</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.5585836179453</v>
       </c>
       <c r="E97">
-        <v>-41.74599557519822</v>
+        <v>-42.52322889031971</v>
       </c>
       <c r="F97">
-        <v>-2.698454178808857</v>
+        <v>-1.921130775369857</v>
       </c>
       <c r="G97">
-        <v>-6.239720693632207</v>
+        <v>-5.760731101737216</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.18783651210188</v>
       </c>
       <c r="E98">
-        <v>-45.02205896164824</v>
+        <v>-44.97207592978858</v>
       </c>
       <c r="F98">
-        <v>-2.756458121087684</v>
+        <v>-1.977716552655091</v>
       </c>
       <c r="G98">
-        <v>-6.493378003396704</v>
+        <v>-5.995796387753166</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.79935891992449</v>
       </c>
       <c r="E99">
-        <v>-47.09855449007343</v>
+        <v>-46.23546130776651</v>
       </c>
       <c r="F99">
-        <v>-3.546260051082456</v>
+        <v>-2.493670988060583</v>
       </c>
       <c r="G99">
-        <v>-7.040104667570723</v>
+        <v>-6.446692690201901</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.39829660385468</v>
       </c>
       <c r="E100">
-        <v>-49.69568641092346</v>
+        <v>-49.41916420259309</v>
       </c>
       <c r="F100">
-        <v>-3.67425772542823</v>
+        <v>-2.731013159575892</v>
       </c>
       <c r="G100">
-        <v>-7.620569101335454</v>
+        <v>-6.297161969284101</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.92753034886543</v>
       </c>
       <c r="E101">
-        <v>-52.14552858255552</v>
+        <v>-51.42567895794073</v>
       </c>
       <c r="F101">
-        <v>-3.939299674525751</v>
+        <v>-3.104287936788391</v>
       </c>
       <c r="G101">
-        <v>-7.244173315702477</v>
+        <v>-6.763674115041579</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.43507237224706</v>
       </c>
       <c r="E102">
-        <v>-53.83163908431997</v>
+        <v>-53.93046850106336</v>
       </c>
       <c r="F102">
-        <v>-4.318881641143165</v>
+        <v>-3.525994870940369</v>
       </c>
       <c r="G102">
-        <v>-7.694973612330574</v>
+        <v>-7.30779869042173</v>
       </c>
     </row>
   </sheetData>
